--- a/clean/asia_pacific_listings_2026-10-15.xlsx
+++ b/clean/asia_pacific_listings_2026-10-15.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M119"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3310,23 +3310,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Beijing Normal University</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>Capital University of Economics and Business</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>International School of Economics and Management</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96DC1B7F3204BD16</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3336,7 +3332,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96DC1B7F3204BD16</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3353,19 +3349,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Capital University of Economics and Business</t>
+          <t>Dongbei University of Finance &amp; Economics</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>International School of Economics and Management</t>
+          <t>Dongbei University Of Finance And Economics</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3375,7 +3371,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3392,19 +3388,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dongbei University of Finance &amp; Economics</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Donghua University</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dongbei University Of Finance And Economics</t>
+          <t>Glorious Sun School of Business and Management</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3431,23 +3431,26 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Donghua University</t>
+          <t>Fudan University</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Glorious Sun School of Business and Management</t>
-        </is>
+          <t>School of Economics</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>46327</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3457,7 +3460,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3484,16 +3487,18 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>46327</v>
+          <t>School of Management</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3503,7 +3508,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3520,28 +3525,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fudan University</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>Harbin Institute of Technology</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>School of Management</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Rolling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3551,7 +3547,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3568,19 +3564,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Harbin Institute of Technology</t>
+          <t>Huazhong University of Science and Technology</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>CV; Job Market Paper; Letters of Reference</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3590,7 +3591,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3607,24 +3608,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Huazhong University of Science and Technology</t>
+          <t>Hunan University</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
+          <t>School of Economics and Trade</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper; Letters of Reference</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3634,7 +3630,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3651,19 +3647,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hunan University</t>
+          <t>Jilin University</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>School of Economics and Trade</t>
+          <t>Business School</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3673,7 +3669,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -3690,19 +3686,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jilin University</t>
+          <t>Lanzhou University of Finance and Economics</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>the Office of Personnel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3712,7 +3708,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -3729,19 +3725,23 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lanzhou University of Finance and Economics</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Nanjing Agricultural University</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>the Office of Personnel</t>
+          <t>College of Finance</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nanjing Agricultural University</t>
+          <t>Nanjing University</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3778,13 +3778,13 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>College of Finance</t>
+          <t>Business School</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nanjing University</t>
+          <t>Nankai University</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3821,13 +3821,13 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>School of Finance</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nankai University</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3864,13 +3864,16 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>School of Finance</t>
-        </is>
+          <t>Peking University HSBC Business School</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>46364</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3880,7 +3883,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -3907,16 +3910,18 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Peking University HSBC Business School</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>46364</v>
+          <t>Guanghua School of Management</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3926,7 +3931,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -3943,7 +3948,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Peking University</t>
+          <t>Renmin University of China</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3953,18 +3958,16 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Guanghua School of Management</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
+          <t>School of Finance, Renmin University of China</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>46357</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3974,7 +3977,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -3991,19 +3994,26 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remin University</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Shanghai Jiao Tong University</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>School of Applied Economics</t>
-        </is>
+          <t>Antai College of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>46341</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=680004BD3C688FB5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4013,7 +4023,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=680004BD3C688FB5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4030,26 +4040,23 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Renmin University of China</t>
+          <t>Shanghai University of Finance Economics School</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>985/211</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>School of Finance, Renmin University of China</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>46357</v>
+          <t>School of Digital Economy</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4059,7 +4066,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4076,7 +4083,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Shanghai Jiao Tong University</t>
+          <t>Shanghai University of Finance and Economics</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4086,16 +4093,13 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Antai College of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>46341</v>
+          <t>School of Economics</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4105,7 +4109,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -4122,23 +4126,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance Economics School</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
+          <t>Southwestern University of Finance and Economics</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>School of Digital Economy</t>
+          <t>School of Economics</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -4165,23 +4165,26 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance and Economics</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
+          <t>School of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>46356</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4191,7 +4194,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -4208,23 +4211,23 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance and Economics</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dishui Lake Advanced Finance Institute</t>
+          <t>Center for International Finance and Economics Research</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5D5B5B1874A95B18</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4234,7 +4237,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5D5B5B1874A95B18</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -4251,19 +4254,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Southwestern University of Finance and Economics</t>
+          <t>University of Electronic Science and Technology of China</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>School of Management and Economics</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4273,7 +4276,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4290,23 +4293,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tongji University</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>nothing</t>
+          <t>Institute of International Finance</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41EFAE6DC817CCD8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4316,7 +4315,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41EFAE6DC817CCD8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -4333,26 +4332,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>46356</v>
+          <t>School of Management</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4362,7 +4354,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -4379,23 +4371,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>Xi%u2019an Jiaotong University</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>School of Social Sciences</t>
+          <t>School of Economics and Finance</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=48673CE5E9319FD6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4405,7 +4393,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=48673CE5E9319FD6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -4422,23 +4410,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>Xi%u2019an Jiaotong-Liverpool University</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Center for International Finance and Economics Research</t>
+          <t>International Business School Suzhou (IBSS), Department of Economics</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4448,7 +4432,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -4465,19 +4449,23 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>University of Electronic Science and Technology of China</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Zhejiang University</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>School of Management and Economics</t>
+          <t>International Business School</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4487,7 +4475,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -4504,19 +4492,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>University of Science and Technology of China</t>
+          <t>Zhongnan Unviersity of Economics and Law</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Institute of International Finance</t>
+          <t>School of Finance</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4526,7 +4514,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -4538,34 +4526,52 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Kowloon Tong, Kowloon</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>University of Science and Technology of China</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>School of Management</t>
-        </is>
+          <t>Economics and Finance</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>46356</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
+          <t>https://econjobmarket.org/positions/12596</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Job Market Paper; Research Statement</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>CICE</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
+          <t>https://econjobmarket.org/positions/12596</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>efpost@cityu.edu.hk</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -4577,34 +4583,47 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Pokfulam Road</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Xi%u2019an Jiaotong University</t>
+          <t>University of Hong Kong</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>School of Economics and Finance</t>
-        </is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>46341</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
+          <t>https://econjobmarket.org/positions/12521</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>CICE</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
+          <t>https://econjobmarket.org/positions/12521</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>orgecon@hku.hk</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -4616,34 +4635,52 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Pokfulam Road</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Xi%u2019an Jiaotong-Liverpool University</t>
+          <t>University of Hong Kong</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>International Business School Suzhou (IBSS), Department of Economics</t>
-        </is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>46356</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
+          <t>https://econjobmarket.org/positions/12581</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Job Market Paper</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>CICE</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
+          <t>https://econjobmarket.org/positions/12581</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>econ.jobmarket@hku.hk</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -4655,38 +4692,51 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Zhejiang University</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>City University of Hong Kong</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>International Business School</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
+          <t>Department of Economics and Finance</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477722 | http://jobs.cityu.edu.hk</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Job Market Paper; Research Statement</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>CICE</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
+          <t>http://jobs.cityu.edu.hk</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>efpost@cityu.edu.hk</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -4698,34 +4748,51 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Zhongnan Unviersity of Economics and Law</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>School of Finance</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>Department of Economics and Finance</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477723 | http://jobs.cityu.edu.hk</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Job Market Paper; Research Statement</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>CICE</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
+          <t>http://jobs.cityu.edu.hk</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>efpost@cityu.edu.hk</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -4737,12 +4804,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Kowloon Tong, Kowloon</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4751,38 +4813,27 @@
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Economics and Finance</t>
-        </is>
-      </c>
       <c r="F86" s="2" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G86" t="inlineStr"/>
+        <v>46418</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12596</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Job Market Paper; Research Statement</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477624 | https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12596</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>efpost@cityu.edu.hk</t>
+          <t>https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -4794,17 +4845,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pokfulam Road</t>
+          <t>Hong Kong, Hong Kong</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>University of Hong Kong</t>
+          <t>Hong Kong University of Science and Technology</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -4814,27 +4865,36 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>46341</v>
-      </c>
-      <c r="G87" t="inlineStr"/>
+        <v>46348</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12521</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477656 | https://apply.interfolio.com/191029</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12521</t>
+          <t>https://apply.interfolio.com/191029</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>orgecon@hku.hk</t>
+          <t>econjob@ust.hk</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -4846,52 +4906,51 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Pokfulam Road</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>University of Hong Kong</t>
+          <t>The Chinese University of Hong Kong</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>Department of Decisions, Operations and Technology</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G88" t="inlineStr"/>
+        <v>46387</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12581</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477636 | http://career.cuhk.edu.hk</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Job Market Paper</t>
+          <t>Teaching Evaluations</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12581</t>
+          <t>http://career.cuhk.edu.hk</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>econ.jobmarket@hku.hk</t>
+          <t>dote@cuhk.edu.hk</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -4908,13 +4967,13 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>The University of Hong Kong</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Department of Economics and Finance</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
@@ -4927,12 +4986,12 @@
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477722 | http://jobs.cityu.edu.hk</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477668 | https://jobs.hku.hk</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Job Market Paper; Research Statement</t>
+          <t>Job Market Paper</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4942,12 +5001,12 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>http://jobs.cityu.edu.hk</t>
+          <t>https://jobs.hku.hk</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>efpost@cityu.edu.hk</t>
+          <t>econ.jobmarket@hku.hk</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -4959,18 +5018,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Tokyo, Tokyo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>Bank of Japan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Department of Economics and Finance</t>
+          <t>Institute for Monetary and Economic Studies (IMES)</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
@@ -4983,12 +5047,12 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477723 | http://jobs.cityu.edu.hk</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Job Market Paper; Research Statement</t>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -4998,12 +5062,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>http://jobs.cityu.edu.hk</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>efpost@cityu.edu.hk</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -5015,12 +5074,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Minato-Ku, Tokyo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>Japan Fair Trade Commission</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -5034,7 +5098,12 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477624 | https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477599 | https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5044,7 +5113,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
+          <t>https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -5056,17 +5125,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Hong Kong, Hong Kong</t>
+          <t>Tokyo, Tokyo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hong Kong University of Science and Technology</t>
+          <t>Musashi University</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -5076,7 +5145,7 @@
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>46348</v>
+        <v>46326</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5085,12 +5154,7 @@
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477656 | https://apply.interfolio.com/191029</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Research Papers</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477561 | https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5100,12 +5164,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>https://apply.interfolio.com/191029</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>econjob@ust.hk</t>
+          <t>https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -5117,22 +5176,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Yushima, Bunkyo, Tokyo</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>The Chinese University of Hong Kong</t>
+          <t>UTokyo Economic Consulting Inc.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Department of Decisions, Operations and Technology</t>
-        </is>
-      </c>
       <c r="F93" s="2" t="n">
-        <v>46387</v>
+        <v>46356</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5141,12 +5200,7 @@
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477636 | http://career.cuhk.edu.hk</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Teaching Evaluations</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477714 | https://utecon.net/en/</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5156,12 +5210,12 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>http://career.cuhk.edu.hk</t>
+          <t>https://utecon.net/en/</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>dote@cuhk.edu.hk</t>
+          <t>recruit@utecon.net</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -5173,22 +5227,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>The University of Hong Kong</t>
+          <t>Waseda University</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Economics</t>
-        </is>
-      </c>
       <c r="F94" s="2" t="n">
-        <v>46356</v>
+        <v>46310</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5197,12 +5251,7 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477668 | https://jobs.hku.hk</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Job Market Paper</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477611 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5212,12 +5261,7 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.hku.hk</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>econ.jobmarket@hku.hk</t>
+          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -5234,22 +5278,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tokyo, Tokyo</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bank of Japan</t>
+          <t>Waseda University</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Institute for Monetary and Economic Studies (IMES)</t>
+          <t>Faculty of Political Science and Economics (FPSE)</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>46356</v>
+        <v>46310</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -5258,12 +5302,7 @@
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Research Papers</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477612 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5273,7 +5312,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
+          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -5285,31 +5324,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>JAPAN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Minato-Ku, Tokyo</t>
+          <t>Kyoto, Kyoto</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Japan Fair Trade Commission</t>
+          <t>Kyoto University</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Institute for Economic Research</t>
+        </is>
+      </c>
       <c r="F96" s="2" t="n">
-        <v>46418</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+        <v>46332</v>
+      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477599 | https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
+          <t>https://econjobmarket.org/positions/12683</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5319,12 +5359,17 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>AEA</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
+          <t>https://econjobmarket.org/positions/12683</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>soumu-jinji@kier.kyoto-u.ac.jp</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -5336,27 +5381,19 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>JAPAN</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Tokyo, Tokyo</t>
+          <t>MACAO; CHINA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Musashi University</t>
+          <t>University of Macau (UM)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Economics</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>46326</v>
+          <t>Department of Finance and Business Economics</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5365,7 +5402,12 @@
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477561 | https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477678 | https://career.admo.um.edu.mo/learn-more</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>CV; Cover Letter; Job Market Paper; Research Papers; Teaching Evaluations; Letters of Reference</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5375,7 +5417,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
+          <t>https://career.admo.um.edu.mo/learn-more</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -5387,46 +5429,47 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>JAPAN</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Yushima, Bunkyo, Tokyo</t>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>UTokyo Economic Consulting Inc.</t>
+          <t>Asia School of Business</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>All departments</t>
+        </is>
+      </c>
       <c r="F98" s="2" t="n">
         <v>46356</v>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477714 | https://utecon.net/en/</t>
+          <t>https://econjobmarket.org/positions/12494</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>CV; Teaching Statement</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>AEA</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>https://utecon.net/en/</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>recruit@utecon.net</t>
+          <t>https://econjobmarket.org/positions/12494</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -5438,22 +5481,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>JAPAN</t>
+          <t>NEW ZEALAND</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Auckland, Auckland</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Waseda University</t>
+          <t>The University of Auckland</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
       <c r="F99" s="2" t="n">
-        <v>46310</v>
+        <v>46321</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5462,7 +5510,12 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477611 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478084 | https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>CV; Cover Letter; Teaching Evaluations</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5472,7 +5525,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
+          <t>https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -5484,27 +5537,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>JAPAN</t>
+          <t>TAIWAN</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Waseda University</t>
+          <t>Institute of Economics, Academia Sinica (IEAS)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Faculty of Political Science and Economics (FPSE)</t>
-        </is>
-      </c>
       <c r="F100" s="2" t="n">
-        <v>46310</v>
+        <v>46357</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5513,7 +5561,12 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477612 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477843 | https://www.econ.sinica.edu.tw/</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Cover Letter; Job Market Paper</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5523,7 +5576,12 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
+          <t>https://www.econ.sinica.edu.tw/</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>searchcommit@econ.sinica.edu.tw</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -5535,52 +5593,56 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TAIWAN</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kyoto, Kyoto</t>
+          <t>Taoyuan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kyoto University</t>
+          <t>National Central University</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Institute for Economic Research</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>46332</v>
-      </c>
-      <c r="G101" t="inlineStr"/>
+        <v>46358</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12683</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Research Papers</t>
+          <t>CV; Cover Letter; Job Market Paper; Transcript</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12683</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>soumu-jinji@kier.kyoto-u.ac.jp</t>
+          <t>ncu66301@ncu.edu.tw</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -5592,19 +5654,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MACAO; CHINA</t>
+          <t>TAIWAN</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Zhongli, Taoyuan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>University of Macau (UM)</t>
+          <t>National Central University</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Department of Finance and Business Economics</t>
-        </is>
+          <t>Graduate Institute of Industrial Economics</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>46368</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5613,12 +5683,7 @@
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477678 | https://career.admo.um.edu.mo/learn-more</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>CV; Cover Letter; Job Market Paper; Research Papers; Teaching Evaluations; Letters of Reference</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5628,7 +5693,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>https://career.admo.um.edu.mo/learn-more</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -5640,47 +5705,56 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>TAIWAN</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, Malaysia</t>
+          <t>Taoyuan City</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Asia School of Business</t>
+          <t>National Central University</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>All departments</t>
+          <t>Department of Finance</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G103" t="inlineStr"/>
+        <v>46402</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12494</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>CV; Teaching Statement</t>
+          <t>Job Market Paper</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12494</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>ncu6250@ncu.edu.tw</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -5692,17 +5766,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>NEW ZEALAND</t>
+          <t>TAIWAN</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Auckland, Auckland</t>
+          <t>Tainan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>The University of Auckland</t>
+          <t>National Cheng Kung University</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -5712,7 +5786,7 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>46321</v>
+        <v>46354</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5721,12 +5795,12 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478084 | https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>CV; Cover Letter; Teaching Evaluations</t>
+          <t>Cover Letter</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5736,7 +5810,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -5758,12 +5832,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Institute of Economics, Academia Sinica (IEAS)</t>
+          <t>National Chengchi University</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Department of Economics</t>
+        </is>
+      </c>
       <c r="F105" s="2" t="n">
-        <v>46357</v>
+        <v>46356</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5772,12 +5851,7 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477843 | https://www.econ.sinica.edu.tw/</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>Cover Letter; Job Market Paper</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5787,12 +5861,12 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>https://www.econ.sinica.edu.tw/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>searchcommit@econ.sinica.edu.tw</t>
+          <t>econ@nccu.edu.tw</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -5809,22 +5883,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Taoyuan</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>National Central University</t>
+          <t>National Chengchi University</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>College of Global Banking and Finance</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>46358</v>
+        <v>46387</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5833,12 +5907,12 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477791 | https://cgbf.nccu.edu.tw/</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CV; Cover Letter; Job Market Paper; Transcript</t>
+          <t>CV; Job Market Paper</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5848,12 +5922,12 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
+          <t>https://cgbf.nccu.edu.tw/</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>ncu66301@ncu.edu.tw</t>
+          <t>pthung@mail3.nccu.tw</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -5870,22 +5944,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Zhongli, Taoyuan</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>National Central University</t>
+          <t>National Chengchi University</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Graduate Institute of Industrial Economics</t>
+          <t>Department of Money and Banking</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>46368</v>
+        <v>46418</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5894,7 +5968,12 @@
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>CV; Cover Letter; Job Market Paper</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -5904,7 +5983,12 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>banking@nccu.edu.tw</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -5921,22 +6005,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Taoyuan City</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>National Central University</t>
+          <t>National Chengchi University</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Department of Finance</t>
+          <t>The Department of International Business</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>46402</v>
+        <v>46458</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -5945,12 +6029,12 @@
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Job Market Paper</t>
+          <t>CV; Cover Letter; Job Market Paper</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5960,12 +6044,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>ncu6250@ncu.edu.tw</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -5982,22 +6061,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tainan</t>
+          <t>Minhsiung, CHIAYI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>National Cheng Kung University</t>
+          <t>National Chung Cheng University</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>46354</v>
+        <v>46418</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6006,12 +6085,12 @@
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Cover Letter</t>
+          <t>Cover Letter; Research Papers; Research Statement; Transcript</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6021,7 +6100,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -6038,22 +6117,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Kaohsiung</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>National Chengchi University</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>National Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
+          <t>Department of Political Economy</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6062,7 +6145,12 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Cover Letter; Job Market Paper; Teaching Statement; Research Statement</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6072,12 +6160,12 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>econ@nccu.edu.tw</t>
+          <t>poleco@mail.nsysu.edu.tw</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -6094,22 +6182,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>New Taipei City</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>National Chengchi University</t>
+          <t>National Taipei University</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>College of Global Banking and Finance</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>46387</v>
+        <v>46366</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6118,12 +6206,7 @@
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477791 | https://cgbf.nccu.edu.tw/</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6133,12 +6216,12 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>https://cgbf.nccu.edu.tw/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>pthung@mail3.nccu.tw</t>
+          <t>econ_job@mail.ntpu.edu.tw; tapply@gm.ntpu.edu.tw</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -6160,13 +6243,13 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>National Chengchi University</t>
+          <t>National Taiwan University</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Department of Money and Banking</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
@@ -6179,12 +6262,7 @@
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>CV; Cover Letter; Job Market Paper</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477929 | https://econ.ntu.edu.tw</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6194,12 +6272,12 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
+          <t>https://econ.ntu.edu.tw</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>banking@nccu.edu.tw</t>
+          <t>kuanmingchen@ntu.edu.tw</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -6216,22 +6294,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Hsinchu</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>National Chengchi University</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>National Tsing Hua University</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>The Department of International Business</t>
+          <t>Taipei School of Economics and Political Science (TSE)</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>46458</v>
+        <v>46341</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6240,12 +6322,7 @@
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>CV; Cover Letter; Job Market Paper</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477721 | https://www.tse.nthu.edu.tw/</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6255,7 +6332,12 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
+          <t>https://www.tse.nthu.edu.tw/</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>tse@my.nthu.edu.tw</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -6272,22 +6354,26 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Minhsiung, CHIAYI</t>
+          <t>Hsinchu City, Hsinchu</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>National Chung Cheng University</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>National Tsing Hua University</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>46418</v>
+        <v>46355</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -6296,12 +6382,7 @@
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>Cover Letter; Research Papers; Research Statement; Transcript</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6311,302 +6392,10 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>TAIWAN</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Kaohsiung</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>National Sun Yat-sen University</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Department of Political Economy</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="n">
-        <v>46387</v>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Cover Letter; Job Market Paper; Teaching Statement; Research Statement</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K115" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>poleco@mail.nsysu.edu.tw</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>TAIWAN</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>New Taipei City</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>National Taipei University</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Department of Economics</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>46366</v>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K116" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>econ_job@mail.ntpu.edu.tw; tapply@gm.ntpu.edu.tw</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>TAIWAN</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Taipei</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>National Taiwan University</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Department of Economics</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>46418</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477929 | https://econ.ntu.edu.tw</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K117" s="3" t="inlineStr">
-        <is>
-          <t>https://econ.ntu.edu.tw</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>kuanmingchen@ntu.edu.tw</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>TAIWAN</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Hsinchu</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>National Tsing Hua University</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Taipei School of Economics and Political Science (TSE)</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>46341</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477721 | https://www.tse.nthu.edu.tw/</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K118" s="3" t="inlineStr">
-        <is>
-          <t>https://www.tse.nthu.edu.tw/</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>tse@my.nthu.edu.tw</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>TAIWAN</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Hsinchu City, Hsinchu</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>National Tsing Hua University</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Economics</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>46355</v>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K119" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
@@ -6840,16 +6629,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId225"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId236"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/clean/asia_pacific_listings_2026-10-15.xlsx
+++ b/clean/asia_pacific_listings_2026-10-15.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M114"/>
+  <dimension ref="A1:M113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>46418</v>
+        <v>46357</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>46402</v>
+        <v>46366</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -3310,19 +3310,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Capital University of Economics and Business</t>
+          <t>Dongbei University of Finance &amp; Economics</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>International School of Economics and Management</t>
+          <t>Dongbei University Of Finance And Economics</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=230A8F8CAE8FB702</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3349,19 +3349,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dongbei University of Finance &amp; Economics</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Donghua University</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dongbei University Of Finance And Economics</t>
+          <t>Glorious Sun School of Business and Management</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3371,7 +3375,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=9058523321C2911A</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3388,23 +3392,26 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Donghua University</t>
+          <t>Fudan University</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Glorious Sun School of Business and Management</t>
-        </is>
+          <t>School of Economics</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>46327</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3414,7 +3421,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=1CE68DDB85B84365</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3441,16 +3448,18 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>46327</v>
+          <t>School of Management</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3460,12 +3469,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E968D280DD59D564</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -3477,28 +3486,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fudan University</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>Harbin Institute of Technology</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>School of Management</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Rolling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=E153FEE8CC8E11B5</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3525,19 +3525,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Harbin Institute of Technology</t>
+          <t>Huazhong University of Science and Technology</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>CV; Job Market Paper; Letters of Reference</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3547,12 +3552,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3ED8A58471D2F80B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -3564,24 +3569,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Huazhong University of Science and Technology</t>
+          <t>Hunan University</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>School of Economics, Huazhong University of Science &amp; Technology</t>
+          <t>School of Economics and Trade</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>CV; Job Market Paper; Letters of Reference</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A380FA8882023C78</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -3608,19 +3608,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hunan University</t>
+          <t>Lanzhou University of Finance and Economics</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>School of Economics and Trade</t>
+          <t>the Office of Personnel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=38CE3CA2770AB83B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3647,19 +3647,23 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jilin University</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>Nanjing Agricultural University</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>College of Finance</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3669,7 +3673,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A4E054BFC7078E2F</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -3686,19 +3690,23 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lanzhou University of Finance and Economics</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Nanjing University</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>the Office of Personnel</t>
+          <t>Business School</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3708,7 +3716,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=003923B6EFE42FFF</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -3725,7 +3733,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nanjing Agricultural University</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3735,13 +3743,16 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>College of Finance</t>
-        </is>
+          <t>Peking University HSBC Business School</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>46364</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3751,7 +3762,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=41CE1E8D1AE20F34</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -3768,7 +3779,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nanjing University</t>
+          <t>Peking University</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3778,13 +3789,18 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>Guanghua School of Management</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3794,7 +3810,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=5EE87D5DE6734D4D</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -3811,7 +3827,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nankai University</t>
+          <t>Renmin University of China</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3821,13 +3837,16 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>School of Finance</t>
-        </is>
+          <t>School of Finance, Renmin University of China</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>46357</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3837,7 +3856,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=96728BEC2B0A48B6</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -3854,26 +3873,28 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Peking University</t>
+          <t>Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>985/211</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Peking University HSBC Business School</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>46364</v>
+          <t>The Shanghai Institute for Mathematics and Interdisciplinary Sciences</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=D6296C379B46AFF9</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3883,7 +3904,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6AA44C52147BF1AA</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=D6296C379B46AFF9</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -3900,28 +3921,26 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Peking University</t>
+          <t>Shanghai Jiao Tong University</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>985/211</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Guanghua School of Management</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
+          <t>Antai College of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>46341</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3931,7 +3950,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=B2D1A3FBC0575542</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -3948,26 +3967,23 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Renmin University of China</t>
+          <t>Shanghai University of Finance and Economics</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>985/211</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>School of Finance, Renmin University of China</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>46357</v>
+          <t>School of Economics</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3977,7 +3993,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A2C98A6CF51DA6B8</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -3994,26 +4010,28 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Shanghai Jiao Tong University</t>
+          <t>Sun Yat-sen University</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Antai College of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>46341</v>
+          <t>Lingnan College</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=73CF283104D9C7BB</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4023,12 +4041,12 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=A718B6651C5FE241</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=73CF283104D9C7BB</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -4040,23 +4058,26 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance Economics School</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>School of Digital Economy</t>
-        </is>
+          <t>School of Economics and Management</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>46356</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4066,7 +4087,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=7E509CEAE1E65959</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4083,23 +4104,23 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Shanghai University of Finance and Economics</t>
+          <t>Tsinghua University</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985/211</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>Center for International Finance and Economics Research</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4109,12 +4130,12 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=3E6981392FF08E75</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -4126,19 +4147,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Southwestern University of Finance and Economics</t>
+          <t>University of Electronic Science and Technology of China</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>School of Economics</t>
+          <t>School of Management and Economics</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4148,12 +4169,12 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=8F2A4E7B41A62BEC</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -4165,26 +4186,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>School of Economics and Management</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>46356</v>
+          <t>Institute of International Finance</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4194,12 +4208,12 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=EB34146E1220A115</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -4211,23 +4225,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tsinghua University</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Center for International Finance and Economics Research</t>
+          <t>School of Management</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4237,7 +4247,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6A1E66715A3A82D9</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -4254,19 +4264,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>University of Electronic Science and Technology of China</t>
+          <t>Xi%u2019an Jiaotong University</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>School of Management and Economics</t>
+          <t>School of Economics and Finance</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4276,7 +4286,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=390B333672086D05</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4293,19 +4303,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>University of Science and Technology of China</t>
+          <t>Xi%u2019an Jiaotong-Liverpool University</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Institute of International Finance</t>
+          <t>International Business School Suzhou (IBSS), Department of Economics</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4315,7 +4325,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=612A2FEECB1FB3D7</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -4332,19 +4342,28 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>University of Science and Technology of China</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Zhejiang University</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>School of Management</t>
+          <t>School of Economics</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7D928B7B1C35099A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4354,7 +4373,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=6CAF00207D46BD36</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=7D928B7B1C35099A</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -4371,19 +4390,23 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Xi%u2019an Jiaotong University</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>Zhejiang University</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>School of Economics and Finance</t>
+          <t>International Business School</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4393,12 +4416,12 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=C3A72C51D391769E</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -4410,19 +4433,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Xi%u2019an Jiaotong-Liverpool University</t>
+          <t>Zhongnan Unviersity of Economics and Law</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>International Business School Suzhou (IBSS), Department of Economics</t>
+          <t>School of Finance</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4432,7 +4455,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=038CBF83FD61166B</t>
+          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -4444,38 +4467,52 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Kowloon Tong, Kowloon</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Zhejiang University</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>City University of Hong Kong</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>International Business School</t>
-        </is>
+          <t>Economics and Finance</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>46356</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
+          <t>https://econjobmarket.org/positions/12596</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Job Market Paper; Research Statement</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>CICE</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=AB6EF80CCC4E40B3</t>
+          <t>https://econjobmarket.org/positions/12596</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>efpost@cityu.edu.hk</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -4487,34 +4524,47 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Pokfulam Road</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Zhongnan Unviersity of Economics and Law</t>
+          <t>University of Hong Kong</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>School of Finance</t>
-        </is>
+          <t>Economics</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>46341</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
+          <t>https://econjobmarket.org/positions/12521</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>CICE</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>http://www.cicecon.org.cn/careers/detail.html?k=2FC3B168FE2DBD23</t>
+          <t>https://econjobmarket.org/positions/12521</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>orgecon@hku.hk</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -4531,18 +4581,18 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kowloon Tong, Kowloon</t>
+          <t>Pokfulam Road</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>University of Hong Kong</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Economics and Finance</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
@@ -4551,12 +4601,12 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12596</t>
+          <t>https://econjobmarket.org/positions/12581</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Job Market Paper; Research Statement</t>
+          <t>Job Market Paper</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4566,12 +4616,12 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12596</t>
+          <t>https://econjobmarket.org/positions/12581</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>efpost@cityu.edu.hk</t>
+          <t>econ.jobmarket@hku.hk</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -4583,47 +4633,51 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Pokfulam Road</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>University of Hong Kong</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>Department of Economics and Finance</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>46341</v>
-      </c>
-      <c r="G82" t="inlineStr"/>
+        <v>46356</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12521</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477722 | http://jobs.cityu.edu.hk</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Job Market Paper; Research Statement</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12521</t>
+          <t>http://jobs.cityu.edu.hk</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>orgecon@hku.hk</t>
+          <t>efpost@cityu.edu.hk</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -4635,52 +4689,51 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Pokfulam Road</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>University of Hong Kong</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>Department of Economics and Finance</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
         <v>46356</v>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12581</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477723 | http://jobs.cityu.edu.hk</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Job Market Paper</t>
+          <t>Job Market Paper; Research Statement</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12581</t>
+          <t>http://jobs.cityu.edu.hk</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>econ.jobmarket@hku.hk</t>
+          <t>efpost@cityu.edu.hk</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -4701,13 +4754,8 @@
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Department of Economics and Finance</t>
-        </is>
-      </c>
       <c r="F84" s="2" t="n">
-        <v>46356</v>
+        <v>46418</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4716,12 +4764,7 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477722 | http://jobs.cityu.edu.hk</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Job Market Paper; Research Statement</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477624 | https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4731,12 +4774,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>http://jobs.cityu.edu.hk</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>efpost@cityu.edu.hk</t>
+          <t>https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -4751,19 +4789,24 @@
           <t>HONG KONG</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Hong Kong, Hong Kong</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>Hong Kong University of Science and Technology</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Department of Economics and Finance</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>46356</v>
+        <v>46348</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4772,12 +4815,12 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477723 | http://jobs.cityu.edu.hk</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477656 | https://apply.interfolio.com/191029</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Job Market Paper; Research Statement</t>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4787,12 +4830,12 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>http://jobs.cityu.edu.hk</t>
+          <t>https://apply.interfolio.com/191029</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>efpost@cityu.edu.hk</t>
+          <t>econjob@ust.hk</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -4809,12 +4852,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>The Chinese University of Hong Kong</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Department of Decisions, Operations and Technology</t>
+        </is>
+      </c>
       <c r="F86" s="2" t="n">
-        <v>46418</v>
+        <v>46387</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4823,7 +4871,12 @@
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477624 | https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477636 | http://career.cuhk.edu.hk</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Teaching Evaluations</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4833,7 +4886,12 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>https://www.cityu.edu.hk/academic/colleges-schools-and-departments</t>
+          <t>http://career.cuhk.edu.hk</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>dote@cuhk.edu.hk</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -4848,14 +4906,9 @@
           <t>HONG KONG</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Hong Kong, Hong Kong</t>
-        </is>
-      </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hong Kong University of Science and Technology</t>
+          <t>The University of Hong Kong</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -4865,7 +4918,7 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>46348</v>
+        <v>46336</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4874,12 +4927,12 @@
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477656 | https://apply.interfolio.com/191029</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477668 | https://jobs.hku.hk</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Research Papers</t>
+          <t>Job Market Paper</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4889,12 +4942,12 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>https://apply.interfolio.com/191029</t>
+          <t>https://jobs.hku.hk</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>econjob@ust.hk</t>
+          <t>econ.jobmarket@hku.hk</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -4906,22 +4959,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Tokyo, Tokyo</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>The Chinese University of Hong Kong</t>
+          <t>Bank of Japan</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Department of Decisions, Operations and Technology</t>
+          <t>Institute for Monetary and Economic Studies (IMES)</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>46387</v>
+        <v>46356</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4930,12 +4988,12 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477636 | http://career.cuhk.edu.hk</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Teaching Evaluations</t>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4945,12 +5003,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>http://career.cuhk.edu.hk</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>dote@cuhk.edu.hk</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -4962,22 +5015,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>JAPAN</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Minato-Ku, Tokyo</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>The University of Hong Kong</t>
+          <t>Japan Fair Trade Commission</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Economics</t>
-        </is>
-      </c>
       <c r="F89" s="2" t="n">
-        <v>46356</v>
+        <v>46418</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4986,12 +5039,12 @@
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477668 | https://jobs.hku.hk</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477599 | https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Job Market Paper</t>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5001,12 +5054,7 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.hku.hk</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>econ.jobmarket@hku.hk</t>
+          <t>https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -5028,17 +5076,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bank of Japan</t>
+          <t>Musashi University</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Institute for Monetary and Economic Studies (IMES)</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>46356</v>
+        <v>46326</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5047,12 +5095,7 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Research Papers</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477561 | https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5062,7 +5105,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477873</t>
+          <t>https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -5079,17 +5122,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Minato-Ku, Tokyo</t>
+          <t>Yushima, Bunkyo, Tokyo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Japan Fair Trade Commission</t>
+          <t>UTokyo Economic Consulting Inc.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="F91" s="2" t="n">
-        <v>46418</v>
+        <v>46356</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5098,12 +5141,7 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477599 | https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Research Papers</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477714 | https://utecon.net/en/</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5113,7 +5151,12 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>https://www.jftc.go.jp/soshiki/recruit/specialty.html</t>
+          <t>https://utecon.net/en/</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>recruit@utecon.net</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -5130,22 +5173,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tokyo, Tokyo</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Musashi University</t>
+          <t>Waseda University</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Economics</t>
-        </is>
-      </c>
       <c r="F92" s="2" t="n">
-        <v>46326</v>
+        <v>46310</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5154,7 +5192,7 @@
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477561 | https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477611 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5164,7 +5202,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>https://jrecin.jst.go.jp/seek/SeekJorDetail/Changelang?id=D126070158&amp;lang=1</t>
+          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -5181,17 +5219,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Yushima, Bunkyo, Tokyo</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>UTokyo Economic Consulting Inc.</t>
+          <t>Waseda University</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Faculty of Political Science and Economics (FPSE)</t>
+        </is>
+      </c>
       <c r="F93" s="2" t="n">
-        <v>46356</v>
+        <v>46310</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5200,7 +5243,7 @@
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477714 | https://utecon.net/en/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477612 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5210,12 +5253,7 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>https://utecon.net/en/</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>recruit@utecon.net</t>
+          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -5227,41 +5265,52 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>JAPAN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Kyoto, Kyoto</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Waseda University</t>
+          <t>Kyoto University</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Institute for Economic Research</t>
+        </is>
+      </c>
       <c r="F94" s="2" t="n">
-        <v>46310</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+        <v>46332</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477611 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
+          <t>https://econjobmarket.org/positions/12683</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Research Papers</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>AEA</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26944/</t>
+          <t>https://econjobmarket.org/positions/12683</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>soumu-jinji@kier.kyoto-u.ac.jp</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -5273,27 +5322,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>JAPAN</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Tokyo</t>
+          <t>MACAO; CHINA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Waseda University</t>
+          <t>University of Macau (UM)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Faculty of Political Science and Economics (FPSE)</t>
+          <t>Department of Finance and Business Economics</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>46310</v>
+        <v>46356</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -5302,7 +5346,12 @@
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477612 | https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477678 | https://career.admo.um.edu.mo/learn-more</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>CV; Cover Letter; Job Market Paper; Research Papers; Teaching Evaluations; Letters of Reference</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5312,7 +5361,7 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>https://www.waseda.jp/fpse/pse/news-en/2026/08/04/26955/</t>
+          <t>https://career.admo.um.edu.mo/learn-more</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -5324,52 +5373,50 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>MALAYSIA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kyoto, Kyoto</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kyoto University</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Institute for Economic Research</t>
+          <t>The South East Asian Central Banks (SEACEN) Research and Training Centre</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>985/211</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>46332</v>
-      </c>
-      <c r="G96" t="inlineStr"/>
+        <v>46418</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12683</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Research Papers</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477702 | https://www.seacen.org/</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12683</t>
+          <t>https://www.seacen.org/</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>soumu-jinji@kier.kyoto-u.ac.jp</t>
+          <t>hr@seacen.org</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -5381,43 +5428,47 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MACAO; CHINA</t>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>University of Macau (UM)</t>
+          <t>Asia School of Business</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Department of Finance and Business Economics</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+          <t>All departments</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477678 | https://career.admo.um.edu.mo/learn-more</t>
+          <t>https://econjobmarket.org/positions/12494</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>CV; Cover Letter; Job Market Paper; Research Papers; Teaching Evaluations; Letters of Reference</t>
+          <t>CV; Teaching Statement</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>AEA</t>
+          <t>EJM</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>https://career.admo.um.edu.mo/learn-more</t>
+          <t>https://econjobmarket.org/positions/12494</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -5429,47 +5480,51 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>NEW ZEALAND</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, Malaysia</t>
+          <t>Auckland, Auckland</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Asia School of Business</t>
+          <t>The University of Auckland</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>All departments</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G98" t="inlineStr"/>
+        <v>46321</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12494</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478084 | https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>CV; Teaching Statement</t>
+          <t>CV; Cover Letter; Teaching Evaluations</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>EJM</t>
+          <t>AEA</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>https://econjobmarket.org/positions/12494</t>
+          <t>https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -5481,27 +5536,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NEW ZEALAND</t>
+          <t>TAIWAN</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Auckland, Auckland</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>The University of Auckland</t>
+          <t>Institute of Economics, Academia Sinica (IEAS)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Economics</t>
-        </is>
-      </c>
       <c r="F99" s="2" t="n">
-        <v>46321</v>
+        <v>46357</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5510,12 +5560,12 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478084 | https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477843 | https://www.econ.sinica.edu.tw/</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>CV; Cover Letter; Teaching Evaluations</t>
+          <t>Cover Letter; Job Market Paper</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5525,7 +5575,12 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/TheUniversityOfAuckland/744000151521321-lecturer-senior-lecturer-economics</t>
+          <t>https://www.econ.sinica.edu.tw/</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>searchcommit@econ.sinica.edu.tw</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -5542,17 +5597,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Taoyuan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Institute of Economics, Academia Sinica (IEAS)</t>
+          <t>National Central University</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Economics</t>
+        </is>
+      </c>
       <c r="F100" s="2" t="n">
-        <v>46357</v>
+        <v>46358</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5561,12 +5621,12 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477843 | https://www.econ.sinica.edu.tw/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Cover Letter; Job Market Paper</t>
+          <t>CV; Cover Letter; Job Market Paper; Transcript</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5576,12 +5636,12 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>https://www.econ.sinica.edu.tw/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>searchcommit@econ.sinica.edu.tw</t>
+          <t>ncu66301@ncu.edu.tw</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -5598,7 +5658,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Taoyuan</t>
+          <t>Zhongli, Taoyuan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5609,11 +5669,11 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>Graduate Institute of Industrial Economics</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>46358</v>
+        <v>46368</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5622,12 +5682,7 @@
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>CV; Cover Letter; Job Market Paper; Transcript</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5637,12 +5692,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477598</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>ncu66301@ncu.edu.tw</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -5659,7 +5709,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Zhongli, Taoyuan</t>
+          <t>Taoyuan City</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5670,11 +5720,11 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Graduate Institute of Industrial Economics</t>
+          <t>Department of Finance</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>46368</v>
+        <v>46402</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5683,7 +5733,12 @@
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Job Market Paper</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5693,7 +5748,12 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477690</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>ncu6250@ncu.edu.tw</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -5710,22 +5770,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Taoyuan City</t>
+          <t>Tainan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>National Central University</t>
+          <t>National Cheng Kung University</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Department of Finance</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>46402</v>
+        <v>46354</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5734,12 +5794,12 @@
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Job Market Paper</t>
+          <t>Cover Letter</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5749,12 +5809,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477637</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>ncu6250@ncu.edu.tw</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -5771,22 +5826,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tainan</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>National Cheng Kung University</t>
+          <t>National Chengchi University</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Economics</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>46354</v>
+        <v>46356</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5795,12 +5850,7 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Cover Letter</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5810,7 +5860,12 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477925</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>econ@nccu.edu.tw</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -5838,11 +5893,11 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
+          <t>College of Global Banking and Finance</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5851,7 +5906,12 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477791 | https://cgbf.nccu.edu.tw/</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>CV; Job Market Paper</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5861,12 +5921,12 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477745</t>
+          <t>https://cgbf.nccu.edu.tw/</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>econ@nccu.edu.tw</t>
+          <t>pthung@mail3.nccu.tw</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -5894,11 +5954,11 @@
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>College of Global Banking and Finance</t>
+          <t>Department of Money and Banking</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>46387</v>
+        <v>46418</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5907,12 +5967,12 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477791 | https://cgbf.nccu.edu.tw/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CV; Job Market Paper</t>
+          <t>CV; Cover Letter; Job Market Paper</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5922,12 +5982,12 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>https://cgbf.nccu.edu.tw/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>pthung@mail3.nccu.tw</t>
+          <t>banking@nccu.edu.tw</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -5955,11 +6015,11 @@
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Department of Money and Banking</t>
+          <t>The Department of International Business</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>46418</v>
+        <v>46458</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5968,7 +6028,7 @@
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5983,12 +6043,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478008</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>banking@nccu.edu.tw</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -6005,22 +6060,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Minhsiung, CHIAYI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>National Chengchi University</t>
+          <t>National Chung Cheng University</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>The Department of International Business</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>46458</v>
+        <v>46418</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6029,12 +6084,12 @@
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>CV; Cover Letter; Job Market Paper</t>
+          <t>Cover Letter; Research Papers; Research Statement; Transcript</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6044,7 +6099,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111478133</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -6061,22 +6116,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Minhsiung, CHIAYI</t>
+          <t>Kaohsiung</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>National Chung Cheng University</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>National Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
+          <t>Department of Political Economy</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>46418</v>
+        <v>46387</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6085,12 +6144,12 @@
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Cover Letter; Research Papers; Research Statement; Transcript</t>
+          <t>Cover Letter; Job Market Paper; Teaching Statement; Research Statement</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6100,7 +6159,12 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477555</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>poleco@mail.nsysu.edu.tw</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -6117,26 +6181,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kaohsiung</t>
+          <t>New Taipei City</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>National Sun Yat-sen University</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
+          <t>National Taipei University</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Department of Political Economy</t>
+          <t>Department of Economics</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>46387</v>
+        <v>46366</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6145,12 +6205,7 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>Cover Letter; Job Market Paper; Teaching Statement; Research Statement</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6160,12 +6215,12 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477532</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>poleco@mail.nsysu.edu.tw</t>
+          <t>econ_job@mail.ntpu.edu.tw; tapply@gm.ntpu.edu.tw</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -6182,12 +6237,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>New Taipei City</t>
+          <t>Taipei</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>National Taipei University</t>
+          <t>National Taiwan University</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -6197,7 +6252,7 @@
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>46366</v>
+        <v>46418</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6206,7 +6261,7 @@
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477929 | https://econ.ntu.edu.tw</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6216,12 +6271,12 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477648</t>
+          <t>https://econ.ntu.edu.tw</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>econ_job@mail.ntpu.edu.tw; tapply@gm.ntpu.edu.tw</t>
+          <t>kuanmingchen@ntu.edu.tw</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -6238,22 +6293,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Taipei</t>
+          <t>Hsinchu</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>National Taiwan University</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>National Tsing Hua University</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>985/211</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Department of Economics</t>
+          <t>Taipei School of Economics and Political Science (TSE)</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>46418</v>
+        <v>46341</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -6262,7 +6321,7 @@
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477929 | https://econ.ntu.edu.tw</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477721 | https://www.tse.nthu.edu.tw/</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6272,12 +6331,12 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>https://econ.ntu.edu.tw</t>
+          <t>https://www.tse.nthu.edu.tw/</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>kuanmingchen@ntu.edu.tw</t>
+          <t>tse@my.nthu.edu.tw</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -6294,7 +6353,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Hsinchu</t>
+          <t>Hsinchu City, Hsinchu</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6309,11 +6368,11 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Taipei School of Economics and Political Science (TSE)</t>
+          <t>Economics</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>46341</v>
+        <v>46355</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6322,7 +6381,7 @@
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477721 | https://www.tse.nthu.edu.tw/</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6332,70 +6391,10 @@
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
-          <t>https://www.tse.nthu.edu.tw/</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>tse@my.nthu.edu.tw</t>
+          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
-        <is>
-          <t>Faculty</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>TAIWAN</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Hsinchu City, Hsinchu</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>National Tsing Hua University</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>985/211</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Economics</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>46355</v>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>AEA</t>
-        </is>
-      </c>
-      <c r="K114" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-02_111477989</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
         <is>
           <t>Faculty</t>
         </is>
@@ -6627,8 +6626,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId223"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId226"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6751,9 +6748,6 @@
           <t>国际商学院</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>45996</v>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>2026</t>
@@ -6811,9 +6805,6 @@
           <t>国际商学院</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>46136</v>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>2026</t>
@@ -6992,6 +6983,9 @@
           <t>经济与管理学院</t>
         </is>
       </c>
+      <c r="F6" s="2" t="n">
+        <v>46341</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>2026</t>
@@ -7407,32 +7401,34 @@
           <t>经济管理学院</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>46091</v>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>中国农业大学2026年度人才招聘启事</t>
+          <t>【诚聘】中国农业大学经济管理学院诚聘天下英才</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>高层次/普通学术岗全年招聘</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://cau.edu.cn/tzgg/7080fc338ac04c4c87c78e37531fef46.htm</t>
+          <t>https://cem.cau.edu.cn/art/2025/12/16/art_56853_1127416.html</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2017062@cau.edu.cn</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -7469,32 +7465,27 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>【诚聘】中国农业大学经济管理学院诚聘天下英才</t>
+          <t>中国农业大学2026年度人才招聘启事</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>高层次/普通学术岗全年招聘</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://cem.cau.edu.cn/art/2025/12/16/art_56853_1127416.html</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2017062@cau.edu.cn</t>
+          <t>https://cau.edu.cn/tzgg/7080fc338ac04c4c87c78e37531fef46.htm</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -7529,9 +7520,6 @@
           <t>经济与管理学院</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
-        <v>46185</v>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>2026</t>
@@ -7585,6 +7573,9 @@
           <t>经济学院</t>
         </is>
       </c>
+      <c r="F16" s="2" t="n">
+        <v>46356</v>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>2026</t>
@@ -7638,6 +7629,9 @@
           <t>经济学院</t>
         </is>
       </c>
+      <c r="F17" s="2" t="n">
+        <v>46356</v>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>2026</t>
@@ -7692,11 +7686,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>商学院</t>
+          <t>经济学院/商学院</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45991</v>
+        <v>46326</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -7705,22 +7699,22 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>中央财经大学商学院2026年度教学科研岗招聘公告</t>
+          <t>中央财经大学2026年度教学科研相关岗位人才招聘公告（第一批）</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>含师资博士后通道</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://bs.cufe.edu.cn/info/1019/10469.htm</t>
+          <t>https://hr.cufe.edu.cn/info/1046/3431.htm</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7752,11 +7746,13 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>金融学院</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>46083</v>
+          <t>经济学院/商学院</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -7765,7 +7761,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>金融学院2026年度博士后研究人员招收简章</t>
+          <t>中央财经大学2026年度人才招聘公告（第三批）</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -7775,17 +7771,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://sf.cufe.edu.cn/info/1104/15771.htm</t>
+          <t>https://www.cufe.edu.cn/info/1186/26673.htm</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -7815,8 +7811,10 @@
           <t>经济学院/商学院</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
-        <v>46085</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -7875,9 +7873,6 @@
           <t>应用经济学/理论经济学/工商管理</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
-        <v>46090</v>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>2026</t>
@@ -7935,9 +7930,6 @@
           <t>应用经济学/理论经济学/工商管理</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
-        <v>46090</v>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>2026</t>
@@ -7992,11 +7984,13 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>管理科学与工程学院</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>46090</v>
+          <t>商学院</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -8005,7 +7999,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>中央财经大学管理科学与工程学院2026年度第一批龙马博士后研究人员招收简章</t>
+          <t>中央财经大学商学院2026年度教学科研岗招聘公告</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -8020,12 +8014,12 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>https://mse.cufe.edu.cn/info/1073/12521.htm</t>
+          <t>https://bs.cufe.edu.cn/info/1019/10469.htm</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -8052,11 +8046,13 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>经济学院/商学院</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>46129</v>
+          <t>商学院、科技商学院</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -8065,7 +8061,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>中央财经大学2026年度人才招聘公告（第三批）</t>
+          <t>中央财经大学商学院、科技商学院2026年度教学科研岗招聘公告（第三批）</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -8075,12 +8071,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://www.cufe.edu.cn/info/1186/26673.htm</t>
+          <t>http://bs.cufe.edu.cn/info/1019/11089.htm</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -8112,11 +8108,8 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>商学院、科技商学院</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>46187</v>
+          <t>管理科学与工程学院</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -8125,7 +8118,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>中央财经大学商学院、科技商学院2026年度教学科研岗招聘公告（第三批）</t>
+          <t>中央财经大学管理科学与工程学院2026年度第一批龙马博士后研究人员招收简章</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -8140,12 +8133,12 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>http://bs.cufe.edu.cn/info/1019/11089.htm</t>
+          <t>https://mse.cufe.edu.cn/info/1073/12521.htm</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -8172,12 +8165,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>经济学院/商学院</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Rolling</t>
+          <t>金融学院</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8187,27 +8175,27 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>中央财经大学2026年度教学科研相关岗位人才招聘公告（第一批）</t>
+          <t>金融学院2026年度博士后研究人员招收简章</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>含师资博士后通道</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://hr.cufe.edu.cn/info/1046/3431.htm</t>
+          <t>https://sf.cufe.edu.cn/info/1104/15771.htm</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -8237,9 +8225,6 @@
           <t>经济管理学院</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n">
-        <v>46143</v>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>2026</t>
@@ -9592,6 +9577,9 @@
           <t>经济学院</t>
         </is>
       </c>
+      <c r="F51" s="2" t="n">
+        <v>46387</v>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" s="3" t="inlineStr">
         <is>
@@ -9904,7 +9892,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>??</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -9919,13 +9907,11 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>经济与管理学院</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>46387</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -9934,12 +9920,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>2026年福州大学高层次专业技术人员招聘方案（含经管）</t>
+          <t>2026年福州大学高层次教学科研人员招聘方案（含经管学院）</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>招满即止</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -9949,7 +9935,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>https://rsc.fzu.edu.cn/info/1071/2642.htm</t>
+          <t>https://rsc.fzu.edu.cn/info/1071/2641.htm</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -9966,7 +9952,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -9981,7 +9967,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>???????</t>
+          <t>经济与管理学院</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -9996,12 +9982,12 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>2026年福州大学高层次教学科研人员招聘方案（含经管学院）</t>
+          <t>2026年福州大学高层次专业技术人员招聘方案（含经管）</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>招满即止</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -10011,7 +9997,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>https://rsc.fzu.edu.cn/info/1071/2641.htm</t>
+          <t>https://rsc.fzu.edu.cn/info/1071/2642.htm</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -11966,9 +11952,6 @@
           <t>人事处</t>
         </is>
       </c>
-      <c r="F94" s="2" t="n">
-        <v>46240</v>
-      </c>
       <c r="G94" t="inlineStr">
         <is>
           <t>2026</t>
@@ -12081,13 +12064,20 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>经济学科</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr"/>
+          <t>国际商学院</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>46387</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>拥抱自贸港，拥有未来｜海南大学经济学科诚聘海内外高层次人才</t>
+          <t>海南大学2026年招聘教学科研专业技术人员公告</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -12102,12 +12092,12 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>http://www.efnchina.com/info/1111/59241.htm</t>
+          <t>https://hro.hainanu.edu.cn/info/1009/9413.htm</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -12137,6 +12127,9 @@
           <t>国际商学院</t>
         </is>
       </c>
+      <c r="F97" s="2" t="n">
+        <v>46387</v>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>2026</t>
@@ -12144,7 +12137,7 @@
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>海南大学2026年全职博士后招收公告</t>
+          <t>海南大学2026年招聘教学科研专业技术人员公告（副本）</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -12159,7 +12152,7 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>https://hro.hainanu.edu.cn/info/1223/9743.htm</t>
+          <t>https://hro.hainanu.edu.cn/info/1074/9473.htm</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -12191,17 +12184,13 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>国际商学院</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+          <t>经济学科</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>海南大学2026年招聘教学科研专业技术人员公告</t>
+          <t>拥抱自贸港，拥有未来｜海南大学经济学科诚聘海内外高层次人才</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12216,12 +12205,12 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>https://hro.hainanu.edu.cn/info/1009/9413.htm</t>
+          <t>http://www.efnchina.com/info/1111/59241.htm</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12247,7 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>海南大学2026年招聘教学科研专业技术人员公告（副本）</t>
+          <t>海南大学2026年全职博士后招收公告</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -12273,7 +12262,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>https://hro.hainanu.edu.cn/info/1074/9473.htm</t>
+          <t>https://hro.hainanu.edu.cn/info/1223/9743.htm</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -12411,16 +12400,17 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>经济学院</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>45873</v>
-      </c>
-      <c r="G102" t="inlineStr"/>
+          <t>人事处</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>河北大学经济学院相关招聘</t>
+          <t>河北大学2026年公开选聘工作人员公告</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -12435,7 +12425,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>https://ec.hbu.edu.cn/info/1084/1669.htm</t>
+          <t>https://rsc.hbu.cn/info/1017/2038.htm</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -12463,17 +12453,13 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>人事处</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>河北大学2026年公开选聘工作人员公告</t>
+          <t>河北大学经济学院相关招聘</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12488,7 +12474,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>https://rsc.hbu.cn/info/1017/2038.htm</t>
+          <t>https://ec.hbu.edu.cn/info/1084/1669.htm</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -12687,7 +12673,7 @@
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>46133</v>
+        <v>46385</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -12696,7 +12682,7 @@
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>江苏大学2026年公开招聘专任教师公告</t>
+          <t>江苏大学2026年公开招聘专任教师公告（高校人才网）</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -12711,7 +12697,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>https://www.ujs.edu.cn/info/1093/211052.htm</t>
+          <t>https://m.gaoxiaojob.com/announcement/detail/395509.html</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -12742,9 +12728,6 @@
           <t>财经学院</t>
         </is>
       </c>
-      <c r="F108" s="2" t="n">
-        <v>46385</v>
-      </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>2026</t>
@@ -12752,7 +12735,7 @@
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>江苏大学2026年公开招聘专任教师公告（高校人才网）</t>
+          <t>江苏大学2026年公开招聘专任教师公告</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -12767,7 +12750,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>https://m.gaoxiaojob.com/announcement/detail/395509.html</t>
+          <t>https://www.ujs.edu.cn/info/1093/211052.htm</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -12799,7 +12782,7 @@
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>46078</v>
+        <v>46387</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -12854,6 +12837,9 @@
           <t>????</t>
         </is>
       </c>
+      <c r="F110" s="2" t="n">
+        <v>46387</v>
+      </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" s="3" t="inlineStr">
         <is>
@@ -13552,6 +13538,9 @@
           <t>经济管理学院</t>
         </is>
       </c>
+      <c r="F122" s="2" t="n">
+        <v>46310</v>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
           <t>2026</t>
@@ -13787,9 +13776,6 @@
           <t>经济管理系</t>
         </is>
       </c>
-      <c r="F126" s="2" t="n">
-        <v>46001</v>
-      </c>
       <c r="G126" t="inlineStr">
         <is>
           <t>2026</t>
@@ -13797,7 +13783,7 @@
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>华北电力大学2026年度教学科研岗位招聘启事（保定）</t>
+          <t>华北电力大学2026年度教学科研岗位招聘启事</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -13812,7 +13798,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>https://www.ncepu.edu.cn/rczp/bdrczp/c9e86b816a9e4c359d3bd2695f737a3a.htm</t>
+          <t>https://www.ncepu.edu.cn/rczp/bjrczp/e5222acc770e4a7cb8e09eefad9098e1.htm</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -13847,9 +13833,6 @@
           <t>经济管理系</t>
         </is>
       </c>
-      <c r="F127" s="2" t="n">
-        <v>46001</v>
-      </c>
       <c r="G127" t="inlineStr">
         <is>
           <t>2026</t>
@@ -13857,7 +13840,7 @@
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>华北电力大学2026年度教学科研岗位招聘启事（经管学院转载）</t>
+          <t>华北电力大学2026年度教学科研岗位招聘启事（保定）</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -13872,7 +13855,7 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>https://business.ncepu.edu.cn/szll2/rczp/9ab45767dd944af290b7e2d4c0b41184.htm</t>
+          <t>https://www.ncepu.edu.cn/rczp/bdrczp/c9e86b816a9e4c359d3bd2695f737a3a.htm</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -13914,7 +13897,7 @@
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>华北电力大学2026年度教学科研岗位招聘启事</t>
+          <t>华北电力大学2026年度教学科研岗位招聘启事（经管学院转载）</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -13929,7 +13912,7 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>https://www.ncepu.edu.cn/rczp/bjrczp/e5222acc770e4a7cb8e09eefad9098e1.htm</t>
+          <t>https://business.ncepu.edu.cn/szll2/rczp/9ab45767dd944af290b7e2d4c0b41184.htm</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -14595,11 +14578,8 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>经济学院</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>45998</v>
+          <t>金融学院</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -14608,7 +14588,7 @@
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>南开大学经济学院2026年教学科研人员招聘启事</t>
+          <t>2026年南开大学青年学科带头人岗位岗位招聘公告（金融学院）</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -14623,7 +14603,7 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>https://economics.nankai.edu.cn/2025/1120/c16001a584393/page.htm</t>
+          <t>https://finance.nankai.edu.cn/2026/0119/c34541a589287/page.htm</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -14655,20 +14635,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>经济学院</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>46009</v>
+          <t>商学院</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>南开大学经济学院2026年人才引进、教职工公开招聘、博士后招收公告</t>
+          <t>南开大学商学院诚聘全球英才</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -14683,7 +14660,7 @@
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>https://economics.nankai.edu.cn/2025/1211/c16001a586532/page.htm</t>
+          <t>https://nbr.nankai.edu.cn/nkglpl/news/view/20251106121718001</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -14715,11 +14692,13 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>金融学院</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>46031</v>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -14728,7 +14707,7 @@
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>金融学院2026年教学科研（副高）岗位招聘公告</t>
+          <t>南开大学经济学院2026年人才引进、教职工公开招聘、博士后招收公告</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -14743,7 +14722,7 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>https://finance.nankai.edu.cn/2025/1219/c34541a587299/page.htm</t>
+          <t>https://economics.nankai.edu.cn/2025/1211/c16001a586532/page.htm</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -14775,7 +14754,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>金融学院</t>
+          <t>经济学院</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -14785,7 +14769,7 @@
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>2026年南开大学青年学科带头人岗位岗位招聘公告（金融学院）</t>
+          <t>南开大学经济学院2026年教学科研人员招聘启事</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -14800,7 +14784,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>https://finance.nankai.edu.cn/2026/0119/c34541a589287/page.htm</t>
+          <t>https://economics.nankai.edu.cn/2025/1120/c16001a584393/page.htm</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -14832,17 +14816,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>商学院</t>
+          <t>金融学院</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>南开大学商学院诚聘全球英才</t>
+          <t>金融学院2026年教学科研（副高）岗位招聘公告</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -14857,7 +14841,7 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>https://nbr.nankai.edu.cn/nkglpl/news/view/20251106121718001</t>
+          <t>https://finance.nankai.edu.cn/2025/1219/c34541a587299/page.htm</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -15494,11 +15478,8 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>经济学院</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="n">
-        <v>45747</v>
+          <t>光华管理学院</t>
+        </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -15507,7 +15488,7 @@
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>2025年北京大学经济学院教学科研岗位招聘启事</t>
+          <t>2025年北京大学光华管理学院教学科研岗位招聘启事</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -15522,12 +15503,12 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>https://hr.pku.edu.cn/rczp/jxky/f5471d5b1df745db9ff270ba2f4fc7db.htm</t>
+          <t>https://hr.pku.edu.cn/rczp/jxky/a92f835c47714f1ababadf98678a5085.htm</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>econ_pku_hr@163.com</t>
+          <t>recruitment@gsm.pku.edu.cn</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -15562,17 +15543,14 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F157" s="2" t="n">
-        <v>45991</v>
-      </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>北京大学经济学院2026年教职招聘通知</t>
+          <t>2025年北京大学经济学院教学科研岗位招聘启事</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -15587,7 +15565,12 @@
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>https://econ.pku.edu.cn/tzgg/50170econ391389.htm</t>
+          <t>https://hr.pku.edu.cn/rczp/jxky/f5471d5b1df745db9ff270ba2f4fc7db.htm</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>econ_pku_hr@163.com</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -15624,12 +15607,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>2025年北京大学光华管理学院教学科研岗位招聘启事</t>
+          <t>2026年北京大学光华管理学院教学科研岗位招聘启事</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -15644,7 +15627,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>https://hr.pku.edu.cn/rczp/jxky/a92f835c47714f1ababadf98678a5085.htm</t>
+          <t>https://hr.pku.edu.cn/rczp/jxky/5a8411beae2c4e8ba518ba4c6efe8794.htm</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -15681,7 +15664,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>光华管理学院</t>
+          <t>经济学院</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -15691,7 +15674,7 @@
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>2026年北京大学光华管理学院教学科研岗位招聘启事</t>
+          <t>2026年北京大学经济学院教学科研岗位招聘启事</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -15706,12 +15689,12 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>https://hr.pku.edu.cn/rczp/jxky/5a8411beae2c4e8ba518ba4c6efe8794.htm</t>
+          <t>https://hr.pku.edu.cn/rczp/jxky/aba345dfa9d040df8b64488f3af5b37a.htm</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>recruitment@gsm.pku.edu.cn</t>
+          <t>econ_pku_hr@163.com</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -15753,7 +15736,7 @@
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>2026年北京大学经济学院教学科研岗位招聘启事</t>
+          <t>北京大学经济学院2026年教职招聘通知</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -15768,12 +15751,7 @@
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>https://hr.pku.edu.cn/rczp/jxky/aba345dfa9d040df8b64488f3af5b37a.htm</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>econ_pku_hr@163.com</t>
+          <t>https://econ.pku.edu.cn/tzgg/50170econ391389.htm</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -16030,11 +16008,11 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>财政金融学院</t>
+          <t>商学院</t>
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>45981</v>
+        <v>46387</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -16043,7 +16021,7 @@
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>中国人民大学财政金融学院2026年度引进人才和教师通知</t>
+          <t>中国人民大学商学院年度教师招聘（滚动至2026-12-31）</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -16058,17 +16036,17 @@
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>https://ifegg.com/html/11188.html</t>
+          <t>https://www.rmbs.ruc.edu.cn/szyky/rczp/ndjszp/97756c032dac49fab16e5a273f0ebf9d.htm</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>cjzonghe@ruc.edu.cn</t>
+          <t>recruitment@rmbs.ruc.edu.cn</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -16095,40 +16073,33 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>财政金融学院/经济学院</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="n">
-        <v>45981</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+          <t>应用经济学院</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>独树一帜走新路 汇聚英才谱新篇——关于中国人民大学2026年度人才引进和教师招聘通知</t>
+          <t>中国人民大学应用经济学院博士后招聘公告</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>含财政金融学院、经济学院等</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>http://hr.ruc.edu.cn/zpxx/c26637043fc8457496f0781066bcad04.htm</t>
+          <t>http://ae.ruc.edu.cn/xwzx/tzgg/62a1d3280023497a9cc7a2c15c5894c7.htm</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -16158,8 +16129,10 @@
           <t>财政金融学院</t>
         </is>
       </c>
-      <c r="F167" s="2" t="n">
-        <v>45981</v>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -16168,7 +16141,7 @@
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>财政金融学院2026年度人才引进和教师招聘通知</t>
+          <t>中国人民大学财政金融学院2026年度引进人才和教师通知</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -16183,7 +16156,7 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>http://sf.ruc.edu.cn/sylm/gg_sy/gg/67fefa2748ef4125aa908c2f3bfed087.htm</t>
+          <t>https://ifegg.com/html/11188.html</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -16193,7 +16166,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -16220,12 +16193,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>商学院</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Rolling</t>
+          <t>财政金融学院/经济学院</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -16235,27 +16203,22 @@
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>中国人民大学商学院年度教师招聘（滚动至2026-12-31）</t>
+          <t>独树一帜走新路 汇聚英才谱新篇——关于中国人民大学2026年度人才引进和教师招聘通知</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>滚动招聘，招满即止</t>
+          <t>含财政金融学院、经济学院等</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>https://www.rmbs.ruc.edu.cn/szyky/rczp/ndjszp/97756c032dac49fab16e5a273f0ebf9d.htm</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>recruitment@rmbs.ruc.edu.cn</t>
+          <t>http://hr.ruc.edu.cn/zpxx/c26637043fc8457496f0781066bcad04.htm</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -16287,18 +16250,27 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>应用经济学院</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr"/>
+          <t>财政金融学院</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>中国人民大学应用经济学院博士后招聘公告</t>
+          <t>财政金融学院2026年度人才引进和教师招聘通知</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>滚动招聘，招满即止</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -16308,12 +16280,17 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>http://ae.ruc.edu.cn/xwzx/tzgg/62a1d3280023497a9cc7a2c15c5894c7.htm</t>
+          <t>http://sf.ruc.edu.cn/sylm/gg_sy/gg/67fefa2748ef4125aa908c2f3bfed087.htm</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>cjzonghe@ruc.edu.cn</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -16608,9 +16585,6 @@
           <t>经济与管理学院</t>
         </is>
       </c>
-      <c r="F175" s="2" t="n">
-        <v>45905</v>
-      </c>
       <c r="G175" t="inlineStr">
         <is>
           <t>2025</t>
@@ -16664,6 +16638,9 @@
           <t>????</t>
         </is>
       </c>
+      <c r="F176" s="2" t="n">
+        <v>46387</v>
+      </c>
       <c r="G176" t="inlineStr">
         <is>
           <t>2026</t>
@@ -16877,16 +16854,20 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>中银科技金融学院</t>
+          <t>安泰经济与管理学院/会计系</t>
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>46356</v>
-      </c>
-      <c r="G180" t="inlineStr"/>
+        <v>46341</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>上海交通大学中银科技金融学院诚聘天下英才</t>
+          <t>会计系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -16901,7 +16882,7 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97786.html</t>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97769.html</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -16933,11 +16914,11 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/信息技术与创新系</t>
+          <t>安泰经济与管理学院/经济系</t>
         </is>
       </c>
       <c r="F181" s="2" t="n">
-        <v>46357</v>
+        <v>46341</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -16946,7 +16927,7 @@
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>信息、技术与创新系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>经济系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -16961,7 +16942,7 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97772.html</t>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97812.html</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -16993,13 +16974,11 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/会计系</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
+          <t>安泰经济与管理学院/金融系</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>46341</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -17008,7 +16987,7 @@
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>会计系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>金融系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -17023,7 +17002,7 @@
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97769.html</t>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97771.html</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -17055,17 +17034,16 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/数据与商务智能系</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
+          <t>中银科技金融学院</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G183" t="inlineStr"/>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>数据与商务智能系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>上海交通大学中银科技金融学院诚聘天下英才</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -17080,7 +17058,7 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97770.html</t>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97786.html</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -17112,13 +17090,20 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr"/>
+          <t>安泰经济与管理学院/数据与商务智能系</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>46356</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>海外优青 | 欢迎依托上海交大安泰经济与管理学院申报</t>
+          <t>数据与商务智能系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -17133,12 +17118,12 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/94461.html</t>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97770.html</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -17165,8 +17150,11 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/管理科学系</t>
-        </is>
+          <t>安泰经济与管理学院/信息技术与创新系</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>46357</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -17175,7 +17163,7 @@
       </c>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>管理科学系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>信息、技术与创新系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -17190,7 +17178,7 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97783.html</t>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97772.html</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -17222,8 +17210,11 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/组织管理系</t>
-        </is>
+          <t>安泰经济与管理学院/管理科学系</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>46357</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -17232,7 +17223,7 @@
       </c>
       <c r="H186" s="3" t="inlineStr">
         <is>
-          <t>组织管理系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>管理科学系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -17247,7 +17238,7 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97785.html</t>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97783.html</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -17279,17 +17270,13 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/经济系</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
+          <t>安泰经济与管理学院</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" s="3" t="inlineStr">
         <is>
-          <t>经济系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>海外优青 | 欢迎依托上海交大安泰经济与管理学院申报</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -17304,12 +17291,12 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97812.html</t>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/94461.html</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -17336,7 +17323,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>安泰经济与管理学院/金融系</t>
+          <t>安泰经济与管理学院/组织管理系</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -17346,7 +17333,7 @@
       </c>
       <c r="H188" s="3" t="inlineStr">
         <is>
-          <t>金融系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
+          <t>组织管理系2027年度招聘——上海交大安泰经管学院诚聘英才</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -17361,7 +17348,7 @@
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>https://www.acem.sjtu.edu.cn/acem/hr/97771.html</t>
+          <t>https://www.acem.sjtu.edu.cn/acem/hr/97785.html</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -17956,13 +17943,19 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F199" s="2" t="n">
-        <v>45991</v>
-      </c>
-      <c r="G199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
-          <t>山东大学经济学院诚聘海内外英才</t>
+          <t>2025年度山东大学经济学院博士后招聘公告</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -17977,12 +17970,12 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>https://www.econ.sdu.edu.cn/info/1284/13146.htm</t>
+          <t>https://www.econ.sdu.edu.cn/info/1284/12952.htm</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -18019,12 +18012,12 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H200" s="3" t="inlineStr">
         <is>
-          <t>2025年度山东大学经济学院博士后招聘公告</t>
+          <t>2026年度山东大学经济学院博士后招聘公告</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -18039,7 +18032,7 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>https://www.econ.sdu.edu.cn/info/1284/12952.htm</t>
+          <t>https://www.econ.sdu.edu.cn/info/1284/13398.htm</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -18081,12 +18074,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
-          <t>2026年度山东大学经济学院博士后招聘公告</t>
+          <t>山东大学经济学院2025年度教师招聘公告</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -18101,12 +18094,12 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>https://www.econ.sdu.edu.cn/info/1284/13398.htm</t>
+          <t>https://www.econ.sdu.edu.cn/info/1284/11073.htm</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -18136,19 +18129,10 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="G202" t="inlineStr"/>
       <c r="H202" s="3" t="inlineStr">
         <is>
-          <t>山东大学经济学院2025年度教师招聘公告</t>
+          <t>山东大学经济学院诚聘海内外英才</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -18163,7 +18147,7 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>https://www.econ.sdu.edu.cn/info/1284/11073.htm</t>
+          <t>https://www.econ.sdu.edu.cn/info/1284/13146.htm</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -18644,6 +18628,9 @@
           <t>经济管理学院</t>
         </is>
       </c>
+      <c r="F211" s="2" t="n">
+        <v>46310</v>
+      </c>
       <c r="G211" t="inlineStr">
         <is>
           <t>2026</t>
@@ -18879,6 +18866,9 @@
           <t>经济管理学院</t>
         </is>
       </c>
+      <c r="F215" s="2" t="n">
+        <v>46540</v>
+      </c>
       <c r="G215" t="inlineStr"/>
       <c r="H215" s="3" t="inlineStr">
         <is>
@@ -19229,12 +19219,16 @@
         </is>
       </c>
       <c r="F221" s="2" t="n">
-        <v>46059</v>
-      </c>
-      <c r="G221" t="inlineStr"/>
+        <v>46387</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="H221" s="3" t="inlineStr">
         <is>
-          <t>天津师范大学数量经济学经济学院教师岗招聘</t>
+          <t>2026年天津师范大学第一批招聘（博士层次专业技术岗位）公告</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -19249,7 +19243,7 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>https://www.sciencehr.net/job/208814.html</t>
+          <t>http://www.jiaoshizhaopin.net/tianjin/jobshow_511040.html</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -19284,17 +19278,10 @@
           <t>经济学院</t>
         </is>
       </c>
-      <c r="F222" s="2" t="n">
-        <v>46387</v>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="G222" t="inlineStr"/>
       <c r="H222" s="3" t="inlineStr">
         <is>
-          <t>2026年天津师范大学第一批招聘（博士层次专业技术岗位）公告</t>
+          <t>天津师范大学数量经济学经济学院教师岗招聘</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -19309,7 +19296,7 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>http://www.jiaoshizhaopin.net/tianjin/jobshow_511040.html</t>
+          <t>https://www.sciencehr.net/job/208814.html</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -19820,25 +19807,22 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>全球创新与治理研究院</t>
-        </is>
-      </c>
-      <c r="F231" s="2" t="n">
-        <v>45646</v>
+          <t>中国金融学院</t>
+        </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H231" s="3" t="inlineStr">
         <is>
-          <t>对外经济贸易大学全球创新与治理研究院2025年专职教学科研人员招聘公告</t>
+          <t>中国金融学院2026年专职教师招聘公告</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>产业经济学方向</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -19848,7 +19832,7 @@
       </c>
       <c r="K231" s="3" t="inlineStr">
         <is>
-          <t>https://agig.uibe.edu.cn/tzgg/e30c29f3c079417eadaaedb5f16dfc54.htm</t>
+          <t>https://sbf.uibe.edu.cn/tzgg/b20abafc23f940349876baa87054aace.htm</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -19880,11 +19864,8 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>中国金融学院</t>
-        </is>
-      </c>
-      <c r="F232" s="2" t="n">
-        <v>45992</v>
+          <t>国际经济贸易学院</t>
+        </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -19893,27 +19874,27 @@
       </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>中国金融学院2026年专职教师招聘公告</t>
+          <t>对外经济贸易大学2026年度事业编专职教学科研人员、师资博士后招聘公告</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>含国际经济贸易学院等经管岗位</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Dept/HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>https://sbf.uibe.edu.cn/tzgg/b20abafc23f940349876baa87054aace.htm</t>
+          <t>https://hr.uibe.edu.cn/jszp/zpxx/654c850954d7459abbde78b5ebc62820.htm</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -19940,25 +19921,18 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>国际经济贸易学院</t>
-        </is>
-      </c>
-      <c r="F233" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+          <t>国际经济贸易学院/中国金融学院/经济学院</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
       <c r="H233" s="3" t="inlineStr">
         <is>
-          <t>对外经济贸易大学2026年度事业编专职教学科研人员、师资博士后招聘公告</t>
+          <t>对外经济贸易大学全球价值链研究院专职教学科研人员招聘相关公告</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>含国际经济贸易学院等经管岗位</t>
+          <t>See announcement page</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -19968,12 +19942,12 @@
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>https://hr.uibe.edu.cn/jszp/zpxx/654c850954d7459abbde78b5ebc62820.htm</t>
+          <t>https://hr.uibe.edu.cn/jszp/zpxx/ed338932d6d94149945898e2ab2429c7.htm</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -20000,31 +19974,32 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>国际经济贸易学院/中国金融学院/经济学院</t>
-        </is>
-      </c>
-      <c r="F234" s="2" t="n">
-        <v>46202</v>
-      </c>
-      <c r="G234" t="inlineStr"/>
+          <t>全球创新与治理研究院</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>对外经济贸易大学全球价值链研究院专职教学科研人员招聘相关公告</t>
+          <t>对外经济贸易大学全球创新与治理研究院2025年专职教学科研人员招聘公告</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>See announcement page</t>
+          <t>产业经济学方向</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Dept/HR</t>
         </is>
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>https://hr.uibe.edu.cn/jszp/zpxx/ed338932d6d94149945898e2ab2429c7.htm</t>
+          <t>https://agig.uibe.edu.cn/tzgg/e30c29f3c079417eadaaedb5f16dfc54.htm</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -20522,6 +20497,9 @@
           <t>嘉庚学院会计与金融学院</t>
         </is>
       </c>
+      <c r="F243" s="2" t="n">
+        <v>46310</v>
+      </c>
       <c r="G243" t="inlineStr">
         <is>
           <t>2026</t>
@@ -20561,7 +20539,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>厦门</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -20576,8 +20554,11 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>?????/????????</t>
-        </is>
+          <t>经济学院/WISE</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="n">
+        <v>46356</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -20586,7 +20567,7 @@
       </c>
       <c r="H244" s="3" t="inlineStr">
         <is>
-          <t>厦门大学2026年博士后招收启事</t>
+          <t>厦门大学WISE/经济学院2026-2027年诚聘海外研究人员（英才网）</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -20601,12 +20582,12 @@
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>https://postdoctor.xmu.edu.cn/info/1061/4196.htm</t>
+          <t>http://www.gaoxiaozp.com/fujian/62361.html</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20599,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>厦门</t>
+          <t>??</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -20633,7 +20614,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>经济学院/WISE</t>
+          <t>?????/????????</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -20643,7 +20624,7 @@
       </c>
       <c r="H245" s="3" t="inlineStr">
         <is>
-          <t>厦门大学WISE/经济学院2026-2027年诚聘海外研究人员（英才网）</t>
+          <t>厦门大学2026年博士后招收启事</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -20658,12 +20639,12 @@
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>http://www.gaoxiaozp.com/fujian/62361.html</t>
+          <t>https://postdoctor.xmu.edu.cn/info/1061/4196.htm</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -21282,7 +21263,7 @@
         </is>
       </c>
       <c r="F257" s="2" t="n">
-        <v>46387</v>
+        <v>46344</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -21291,7 +21272,7 @@
       </c>
       <c r="H257" s="3" t="inlineStr">
         <is>
-          <t>浙江理工大学2026年特殊专业技术岗位招聘</t>
+          <t>浙江理工大学2026年人才招聘公告</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -21306,12 +21287,12 @@
       </c>
       <c r="K257" s="3" t="inlineStr">
         <is>
-          <t>https://www.gaoxiaojob.com/announcement/detail/432389.html</t>
+          <t>https://news.zstu.edu.cn/info/1113/51843.htm</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Postdoc</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -21337,6 +21318,9 @@
           <t>经济管理学院</t>
         </is>
       </c>
+      <c r="F258" s="2" t="n">
+        <v>46387</v>
+      </c>
       <c r="G258" t="inlineStr">
         <is>
           <t>2026</t>
@@ -21344,7 +21328,7 @@
       </c>
       <c r="H258" s="3" t="inlineStr">
         <is>
-          <t>浙江理工大学2026年人才招聘公告</t>
+          <t>浙江理工大学2026年特殊专业技术岗位招聘</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -21359,12 +21343,12 @@
       </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>https://news.zstu.edu.cn/info/1113/51843.htm</t>
+          <t>https://www.gaoxiaojob.com/announcement/detail/432389.html</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Postdoc</t>
         </is>
       </c>
     </row>
@@ -21663,7 +21647,7 @@
         </is>
       </c>
       <c r="F264" s="2" t="n">
-        <v>46305</v>
+        <v>46326</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -22399,7 +22383,7 @@
         </is>
       </c>
       <c r="F277" s="2" t="n">
-        <v>46353</v>
+        <v>46418</v>
       </c>
       <c r="G277" t="inlineStr"/>
       <c r="H277" s="3" t="inlineStr">
